--- a/ig/DM-MARS-2026/ValueSet-JDV-J238-TypeOffre-ROR.xlsx
+++ b/ig/DM-MARS-2026/ValueSet-JDV-J238-TypeOffre-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="615">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260223120000</t>
+    <t>20260330120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T12:00:00+01:00</t>
+    <t>2026-03-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -102,13 +102,13 @@
     <t>01</t>
   </si>
   <si>
-    <t>Appartement thérapeutique</t>
+    <t>Appartement thérapeutique en psychiatrie</t>
   </si>
   <si>
     <t>02</t>
   </si>
   <si>
-    <t>Atelier thérapeutique</t>
+    <t>Atelier thérapeutique en psychiatrie</t>
   </si>
   <si>
     <t>03</t>
@@ -174,7 +174,7 @@
     <t>13</t>
   </si>
   <si>
-    <t>Service d'Accueil Familial Thérapeutique</t>
+    <t>Service d'Accueil Familial Thérapeutique en psychiatrie</t>
   </si>
   <si>
     <t>14</t>
@@ -216,7 +216,7 @@
     <t>20</t>
   </si>
   <si>
-    <t>Unité d'urgences</t>
+    <t>Unité d'urgences polyvalentes</t>
   </si>
   <si>
     <t>21</t>
@@ -486,7 +486,7 @@
     <t>66</t>
   </si>
   <si>
-    <t>Equipe Relai Handicap rare</t>
+    <t>Equipe Relais Handicaps Rares (ERHR)</t>
   </si>
   <si>
     <t>67</t>
@@ -951,12 +951,6 @@
     <t>Unité de prise en charge des brûlés</t>
   </si>
   <si>
-    <t>147</t>
-  </si>
-  <si>
-    <t>Unité de sevrage complexe</t>
-  </si>
-  <si>
     <t>148</t>
   </si>
   <si>
@@ -1617,12 +1611,6 @@
     <t>Point d'information local dédié aux personnes âgées</t>
   </si>
   <si>
-    <t>261</t>
-  </si>
-  <si>
-    <t>Accueil familial pour personne âgée</t>
-  </si>
-  <si>
     <t>262</t>
   </si>
   <si>
@@ -1849,12 +1837,6 @@
   </si>
   <si>
     <t>Equipe de Diagnostic de Proximité – Autisme (PDAP, EDAP)</t>
-  </si>
-  <si>
-    <t>300</t>
-  </si>
-  <si>
-    <t>Equipe Mobile de Psychiatrie Périnatale</t>
   </si>
   <si>
     <t>301</t>
@@ -2137,7 +2119,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B298"/>
+  <dimension ref="A1:B295"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -4493,39 +4475,15 @@
         <v>612</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="B295" t="s" s="2">
         <v>614</v>
-      </c>
-      <c r="B295" t="s" s="2">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="B296" t="s" s="2">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="B297" t="s" s="2">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="B298" t="s" s="2">
-        <v>620</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM-MARS-2026/ValueSet-JDV-J238-TypeOffre-ROR.xlsx
+++ b/ig/DM-MARS-2026/ValueSet-JDV-J238-TypeOffre-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="623">
   <si>
     <t>Property</t>
   </si>
@@ -1849,6 +1849,30 @@
   </si>
   <si>
     <t>Centre d’Accueil et de Crise (CAC)</t>
+  </si>
+  <si>
+    <t>303</t>
+  </si>
+  <si>
+    <t>Cabinet de ville infirmier en pratique avancée en pathologies chroniques stabilisées</t>
+  </si>
+  <si>
+    <t>304</t>
+  </si>
+  <si>
+    <t>Cabinet de ville infirmier en pratique avancée en oncologie et hémato-oncologie</t>
+  </si>
+  <si>
+    <t>305</t>
+  </si>
+  <si>
+    <t>Cabinet de ville infirmier en pratique avancée en maladie rénale chronique</t>
+  </si>
+  <si>
+    <t>306</t>
+  </si>
+  <si>
+    <t>Cabinet de ville infirmier en pratique avancée en santé mentale</t>
   </si>
   <si>
     <t/>
@@ -2119,7 +2143,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B295"/>
+  <dimension ref="A1:B299"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -4475,15 +4499,47 @@
         <v>612</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="B296" t="s" s="2">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="B297" t="s" s="2">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="B298" t="s" s="2">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="B299" t="s" s="2">
+        <v>622</v>
       </c>
     </row>
   </sheetData>
